--- a/NR1L_CPAA_Certification.xlsx
+++ b/NR1L_CPAA_Certification.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leyoyylin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDB17B66-1D3D-4713-BF0D-A9A8E90B50C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF45B1C3-9614-473D-8178-9E6AA0471542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-60" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CarPlay Certification" sheetId="2" r:id="rId1"/>
     <sheet name="Android Auto Certification" sheetId="3" r:id="rId2"/>
-    <sheet name="Test Vehicle Usage Plan" sheetId="4" r:id="rId3"/>
+    <sheet name="Test Vehicle Usage Plan" sheetId="4" state="hidden" r:id="rId3"/>
     <sheet name="chang log" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0" iterateDelta="1E-4"/>
@@ -4674,17 +4674,17 @@
         <v>85</v>
       </c>
       <c r="BF21" s="27"/>
-      <c r="BG21" s="27"/>
+      <c r="BG21" s="39" t="s">
+        <v>86</v>
+      </c>
       <c r="BH21" s="27"/>
       <c r="BI21" s="27"/>
-      <c r="BJ21" s="39" t="s">
-        <v>86</v>
-      </c>
+      <c r="BJ21" s="29"/>
       <c r="BK21" s="27"/>
-      <c r="BL21" s="27"/>
-      <c r="BM21" s="27"/>
-      <c r="BN21" s="27"/>
-      <c r="BO21" s="27"/>
+      <c r="BL21" s="31"/>
+      <c r="BM21" s="31"/>
+      <c r="BN21" s="31"/>
+      <c r="BO21" s="31"/>
       <c r="BP21" s="6"/>
       <c r="BQ21" s="6"/>
       <c r="BR21" s="6"/>
